--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127504340</v>
       </c>
       <c r="B2" t="n">
-        <v>109009</v>
+        <v>109011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127504340</v>
       </c>
       <c r="B2" t="n">
-        <v>109011</v>
+        <v>109013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127504340</v>
       </c>
       <c r="B2" t="n">
-        <v>109013</v>
+        <v>109019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127504340</v>
       </c>
       <c r="B2" t="n">
-        <v>109019</v>
+        <v>109022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127504340</v>
       </c>
       <c r="B2" t="n">
-        <v>109022</v>
+        <v>109030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127504340</v>
       </c>
       <c r="B2" t="n">
-        <v>109030</v>
+        <v>109031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127504340</v>
       </c>
       <c r="B2" t="n">
-        <v>109031</v>
+        <v>109032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127504340</v>
       </c>
       <c r="B2" t="n">
-        <v>109032</v>
+        <v>109033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127504340</v>
       </c>
       <c r="B2" t="n">
-        <v>109033</v>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,6 +777,123 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102666459</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gärdesvägen, Mora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>463682</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6771343</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13717-2023 artfynd.xlsx
+++ b/artfynd/A 13717-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102666459</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127504340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>